--- a/docs/oc-mensuales/administracion-y-entrega-de-beneficios/abr-2026.xlsx
+++ b/docs/oc-mensuales/administracion-y-entrega-de-beneficios/abr-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>11137.27</v>
+        <v>10782.14</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>9249.280000000001</v>
+        <v>8954.35</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>79353.03999999999</v>
+        <v>76822.72</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>919.75</v>
+        <v>890.42</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>21769.29</v>
+        <v>21075.14</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>1583.72</v>
+        <v>1533.22</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>1114.28</v>
+        <v>1078.74</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>10721.27</v>
+        <v>10379.4</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>3332.27</v>
+        <v>3226.02</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>58192.23</v>
+        <v>56336.66</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>1293.71</v>
+        <v>1252.45</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>31741.22</v>
+        <v>30729.09</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>196.02</v>
+        <v>189.77</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>541.72</v>
+        <v>524.4400000000001</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>2227.45</v>
+        <v>2156.43</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>289.98</v>
+        <v>280.73</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>20894.93</v>
+        <v>20228.65</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>76847.14999999999</v>
+        <v>75331.62</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>372.43</v>
+        <v>365.09</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>60428.06</v>
+        <v>59236.33</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>26969.88</v>
+        <v>26437.99</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>4894.22</v>
+        <v>4797.7</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>50288.67</v>
+        <v>49296.9</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>18876.02</v>
+        <v>18503.76</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>10569.55</v>
+        <v>10361.1</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>33524.29</v>
+        <v>32863.15</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>1984.35</v>
+        <v>1945.22</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>6390.57</v>
+        <v>6264.54</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>29134.54</v>
+        <v>28559.97</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>972.2</v>
+        <v>953.03</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>26000.29</v>
+        <v>25487.53</v>
       </c>
     </row>
     <row r="33">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>102694.53</v>
+        <v>100669.25</v>
       </c>
     </row>
     <row r="34">
@@ -2525,7 +2525,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>602.12</v>
+        <v>590.24</v>
       </c>
     </row>
     <row r="35">
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>24501.99</v>
+        <v>23856.77</v>
       </c>
     </row>
     <row r="36">
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>14963.55</v>
+        <v>14569.51</v>
       </c>
     </row>
     <row r="37">
@@ -2708,7 +2708,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>140394.38</v>
+        <v>136697.33</v>
       </c>
     </row>
     <row r="38">
@@ -2769,7 +2769,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>13869.64</v>
+        <v>13504.41</v>
       </c>
     </row>
     <row r="39">
@@ -2830,7 +2830,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>19331.46</v>
+        <v>18822.4</v>
       </c>
     </row>
     <row r="40">
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>69912.14999999999</v>
+        <v>68071.13</v>
       </c>
     </row>
     <row r="41">
@@ -2952,7 +2952,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>2297.85</v>
+        <v>2237.34</v>
       </c>
     </row>
     <row r="42">
@@ -3013,7 +3013,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>3369.02</v>
+        <v>3280.31</v>
       </c>
     </row>
     <row r="43">
@@ -3074,7 +3074,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>7796.09</v>
+        <v>7590.79</v>
       </c>
     </row>
     <row r="44">
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>8416.709999999999</v>
+        <v>8195.07</v>
       </c>
     </row>
     <row r="45">
@@ -3196,7 +3196,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>12857.73</v>
+        <v>12519.15</v>
       </c>
     </row>
     <row r="46">
@@ -3257,7 +3257,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>4777.89</v>
+        <v>4652.07</v>
       </c>
     </row>
     <row r="47">
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>22272.92</v>
+        <v>21686.4</v>
       </c>
     </row>
     <row r="48">
@@ -3379,7 +3379,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>1176.1</v>
+        <v>1145.13</v>
       </c>
     </row>
     <row r="49">
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>15068.73</v>
+        <v>14671.92</v>
       </c>
     </row>
     <row r="50">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>3114.51</v>
+        <v>3058.03</v>
       </c>
     </row>
     <row r="51">
@@ -3562,7 +3562,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>863.36</v>
+        <v>847.7</v>
       </c>
     </row>
     <row r="52">
@@ -3623,7 +3623,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>22218.85</v>
+        <v>21815.92</v>
       </c>
     </row>
     <row r="53">
@@ -3684,7 +3684,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>6727.94</v>
+        <v>6605.93</v>
       </c>
     </row>
     <row r="54">
@@ -3745,7 +3745,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>17220.67</v>
+        <v>16908.37</v>
       </c>
     </row>
     <row r="55">
@@ -3806,7 +3806,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>1058.04</v>
+        <v>1038.85</v>
       </c>
     </row>
     <row r="56">
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>5184.39</v>
+        <v>5090.37</v>
       </c>
     </row>
     <row r="57">
@@ -3928,7 +3928,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>6451.47</v>
+        <v>6334.47</v>
       </c>
     </row>
     <row r="58">
@@ -3989,7 +3989,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>264.76</v>
+        <v>259.96</v>
       </c>
     </row>
     <row r="59">
@@ -4050,7 +4050,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>3489.08</v>
+        <v>3425.81</v>
       </c>
     </row>
     <row r="60">
@@ -4111,7 +4111,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>755.4400000000001</v>
+        <v>741.74</v>
       </c>
     </row>
     <row r="61">
@@ -4176,7 +4176,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>509807.31</v>
+        <v>500562.02</v>
       </c>
     </row>
     <row r="62">
@@ -4237,7 +4237,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>12590.68</v>
+        <v>12362.35</v>
       </c>
     </row>
     <row r="63">
@@ -4298,7 +4298,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>880.9</v>
+        <v>857.3099999999999</v>
       </c>
     </row>
     <row r="64">
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>7833.73</v>
+        <v>7623.97</v>
       </c>
     </row>
     <row r="65">
@@ -4420,7 +4420,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>25652.19</v>
+        <v>24965.32</v>
       </c>
     </row>
     <row r="66">
@@ -4481,7 +4481,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>24992.03</v>
+        <v>24322.83</v>
       </c>
     </row>
     <row r="67">
@@ -4542,7 +4542,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>29968.36</v>
+        <v>29165.91</v>
       </c>
     </row>
     <row r="68">
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>434.35</v>
+        <v>422.72</v>
       </c>
     </row>
     <row r="69">
@@ -4664,7 +4664,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>77738.14</v>
+        <v>75656.58</v>
       </c>
     </row>
     <row r="70">
@@ -4725,7 +4725,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>21734.8</v>
+        <v>21152.82</v>
       </c>
     </row>
     <row r="71">
@@ -4786,7 +4786,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>10261.93</v>
+        <v>9987.16</v>
       </c>
     </row>
     <row r="72">
@@ -4847,7 +4847,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>74062.84</v>
+        <v>72079.69</v>
       </c>
     </row>
     <row r="73">
@@ -4908,7 +4908,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>2689.18</v>
+        <v>2617.17</v>
       </c>
     </row>
     <row r="74">
@@ -4969,7 +4969,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>12590.68</v>
+        <v>12253.55</v>
       </c>
     </row>
     <row r="75">
@@ -5030,7 +5030,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>1837.65</v>
+        <v>1788.44</v>
       </c>
     </row>
     <row r="76">
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>339.63</v>
+        <v>330.54</v>
       </c>
     </row>
     <row r="77">
@@ -5152,7 +5152,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>593.5599999999999</v>
+        <v>577.67</v>
       </c>
     </row>
     <row r="78">
@@ -5213,7 +5213,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>10861.84</v>
+        <v>10571</v>
       </c>
     </row>
     <row r="79">
@@ -5274,7 +5274,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>1255.89</v>
+        <v>1222.27</v>
       </c>
     </row>
     <row r="80">
@@ -5335,7 +5335,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>904.62</v>
+        <v>880.4</v>
       </c>
     </row>
     <row r="81">
@@ -5396,7 +5396,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>628.48</v>
+        <v>611.65</v>
       </c>
     </row>
     <row r="82">
@@ -5457,7 +5457,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>993.5</v>
+        <v>996.39</v>
       </c>
     </row>
     <row r="83">
@@ -5518,7 +5518,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>33411.81</v>
+        <v>33509.07</v>
       </c>
     </row>
     <row r="84">
@@ -5579,7 +5579,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>34461.83</v>
+        <v>34562.15</v>
       </c>
     </row>
     <row r="85">
@@ -5640,7 +5640,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>22218.85</v>
+        <v>22283.53</v>
       </c>
     </row>
     <row r="86">
@@ -5701,7 +5701,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>2337.21</v>
+        <v>2344.02</v>
       </c>
     </row>
     <row r="87">
@@ -5762,7 +5762,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>862.3</v>
+        <v>864.8099999999999</v>
       </c>
     </row>
     <row r="88">
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>13383.9</v>
+        <v>13422.86</v>
       </c>
     </row>
     <row r="89">
@@ -5884,7 +5884,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>14902.5</v>
+        <v>14945.88</v>
       </c>
     </row>
     <row r="90">
@@ -5945,7 +5945,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>470.44</v>
+        <v>471.81</v>
       </c>
     </row>
     <row r="91">
@@ -6006,7 +6006,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>8813.48</v>
+        <v>8839.129999999999</v>
       </c>
     </row>
     <row r="92">
@@ -6067,7 +6067,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>8976.99</v>
+        <v>9014.299999999999</v>
       </c>
     </row>
     <row r="93">
@@ -6128,7 +6128,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>18866.98</v>
+        <v>18945.39</v>
       </c>
     </row>
     <row r="94">
@@ -6189,7 +6189,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>2962.51</v>
+        <v>2974.83</v>
       </c>
     </row>
     <row r="95">
@@ -6250,7 +6250,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>1058.04</v>
+        <v>1062.44</v>
       </c>
     </row>
     <row r="96">
@@ -6311,7 +6311,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>863.36</v>
+        <v>866.95</v>
       </c>
     </row>
     <row r="97">
@@ -6372,7 +6372,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>61377.99</v>
+        <v>61633.08</v>
       </c>
     </row>
     <row r="98">
@@ -6433,7 +6433,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>859.66</v>
+        <v>863.23</v>
       </c>
     </row>
     <row r="99">
@@ -6494,7 +6494,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>36289.95</v>
+        <v>36440.77</v>
       </c>
     </row>
     <row r="100">
@@ -6555,7 +6555,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>49153.92</v>
+        <v>49358.2</v>
       </c>
     </row>
     <row r="101">
@@ -6616,7 +6616,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>11653.94</v>
+        <v>11702.37</v>
       </c>
     </row>
     <row r="102">
@@ -6677,7 +6677,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>1603.77</v>
+        <v>1610.43</v>
       </c>
     </row>
     <row r="103">
@@ -6738,7 +6738,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>37885.36</v>
+        <v>38042.82</v>
       </c>
     </row>
     <row r="104">
@@ -6799,7 +6799,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>3341.18</v>
+        <v>3355.07</v>
       </c>
     </row>
     <row r="105">
@@ -6860,7 +6860,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>2646.22</v>
+        <v>2668.67</v>
       </c>
     </row>
     <row r="106">
@@ -6921,7 +6921,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>2940.24</v>
+        <v>2965.19</v>
       </c>
     </row>
     <row r="107">
@@ -6982,7 +6982,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>2646.22</v>
+        <v>2668.67</v>
       </c>
     </row>
     <row r="108">
@@ -7043,7 +7043,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>3118.44</v>
+        <v>3144.9</v>
       </c>
     </row>
     <row r="109">
@@ -7104,7 +7104,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>11135.63</v>
+        <v>11230.14</v>
       </c>
     </row>
     <row r="110">
@@ -7165,7 +7165,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>24425.92</v>
+        <v>24633.23</v>
       </c>
     </row>
     <row r="111">
@@ -7226,7 +7226,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>14627.41</v>
+        <v>14751.55</v>
       </c>
     </row>
     <row r="112">
@@ -7287,7 +7287,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>2723.36</v>
+        <v>2746.48</v>
       </c>
     </row>
     <row r="113">
@@ -7348,7 +7348,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>4025.24</v>
+        <v>4059.4</v>
       </c>
     </row>
     <row r="114">
@@ -7409,7 +7409,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>946.67</v>
+        <v>954.7</v>
       </c>
     </row>
     <row r="115">
@@ -7470,7 +7470,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>890.98</v>
+        <v>898.54</v>
       </c>
     </row>
     <row r="116">
@@ -7531,7 +7531,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>38016.98</v>
+        <v>37953.42</v>
       </c>
     </row>
     <row r="117">
@@ -7592,7 +7592,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>9477.370000000001</v>
+        <v>9461.52</v>
       </c>
     </row>
     <row r="118">
@@ -7653,7 +7653,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>13460.77</v>
+        <v>13438.26</v>
       </c>
     </row>
     <row r="119">
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>12828.74</v>
+        <v>12807.29</v>
       </c>
     </row>
     <row r="120">
@@ -7775,7 +7775,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>9687.42</v>
+        <v>9671.219999999999</v>
       </c>
     </row>
     <row r="121">
@@ -7836,7 +7836,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>53448.08</v>
+        <v>53358.72</v>
       </c>
     </row>
     <row r="122">
@@ -7897,7 +7897,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>8455.860000000001</v>
+        <v>8441.719999999999</v>
       </c>
     </row>
     <row r="123">
@@ -7958,7 +7958,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>46775.64</v>
+        <v>46697.43</v>
       </c>
     </row>
     <row r="124">
@@ -8019,7 +8019,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>18282.94</v>
+        <v>18252.37</v>
       </c>
     </row>
     <row r="125">
@@ -8080,7 +8080,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>26396</v>
+        <v>26351.86</v>
       </c>
     </row>
     <row r="126">
@@ -8141,7 +8141,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>1049.13</v>
+        <v>1047.38</v>
       </c>
     </row>
     <row r="127">
@@ -8202,7 +8202,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>41552.43</v>
+        <v>41482.95</v>
       </c>
     </row>
     <row r="128">
@@ -8263,7 +8263,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>14717.45</v>
+        <v>14692.85</v>
       </c>
     </row>
     <row r="129">
@@ -8324,7 +8324,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>26268.5</v>
+        <v>26224.58</v>
       </c>
     </row>
     <row r="130">
@@ -8385,7 +8385,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>2776.25</v>
+        <v>2771.6</v>
       </c>
     </row>
     <row r="131">
@@ -8446,7 +8446,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>5206.62</v>
+        <v>5197.91</v>
       </c>
     </row>
     <row r="132">
@@ -8507,7 +8507,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>3341.18</v>
+        <v>3335.6</v>
       </c>
     </row>
     <row r="133">
@@ -8568,7 +8568,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>3341.18</v>
+        <v>3335.59</v>
       </c>
     </row>
     <row r="134">
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>24734.87</v>
+        <v>24693.51</v>
       </c>
     </row>
     <row r="135">
@@ -8690,7 +8690,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>32706.15</v>
+        <v>32651.46</v>
       </c>
     </row>
     <row r="136">
@@ -8751,7 +8751,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>10805.38</v>
+        <v>10787.31</v>
       </c>
     </row>
     <row r="137">
@@ -8812,7 +8812,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>7824.21</v>
+        <v>7811.13</v>
       </c>
     </row>
     <row r="138">
@@ -8873,7 +8873,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>891.76</v>
+        <v>890.27</v>
       </c>
     </row>
     <row r="139">
@@ -8934,7 +8934,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>4851.39</v>
+        <v>4911.1</v>
       </c>
     </row>
     <row r="140">
@@ -8995,7 +8995,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>16979.88</v>
+        <v>17188.86</v>
       </c>
     </row>
     <row r="141">
@@ -9056,7 +9056,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>40183.27</v>
+        <v>40677.81</v>
       </c>
     </row>
     <row r="142">
@@ -9117,7 +9117,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>25947.61</v>
+        <v>26266.95</v>
       </c>
     </row>
     <row r="143">
@@ -9178,7 +9178,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>17053.39</v>
+        <v>17263.27</v>
       </c>
     </row>
     <row r="144">
@@ -9239,7 +9239,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>111.23</v>
+        <v>112.6</v>
       </c>
     </row>
     <row r="145">
@@ -9300,7 +9300,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>11405.68</v>
+        <v>11546.05</v>
       </c>
     </row>
     <row r="146">
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>78.41</v>
+        <v>79.37</v>
       </c>
     </row>
     <row r="147">
@@ -9422,7 +9422,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>37681.06</v>
+        <v>38144.81</v>
       </c>
     </row>
     <row r="148">
@@ -9483,7 +9483,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>5494.42</v>
+        <v>5562.04</v>
       </c>
     </row>
     <row r="149">
@@ -9544,7 +9544,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>4345.58</v>
+        <v>4399.07</v>
       </c>
     </row>
     <row r="150">
@@ -9605,7 +9605,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>46500.35</v>
+        <v>47072.65</v>
       </c>
     </row>
     <row r="151">
@@ -9666,7 +9666,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>1396.61</v>
+        <v>1413.8</v>
       </c>
     </row>
     <row r="152">
@@ -9727,7 +9727,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>1113.73</v>
+        <v>1127.43</v>
       </c>
     </row>
     <row r="153">
@@ -9788,7 +9788,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>17005.75</v>
+        <v>17215.05</v>
       </c>
     </row>
     <row r="154">
@@ -9849,7 +9849,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>612</v>
+        <v>619.53</v>
       </c>
     </row>
     <row r="155">
@@ -9910,7 +9910,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>78.23</v>
+        <v>79.19</v>
       </c>
     </row>
     <row r="156">
@@ -9971,7 +9971,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>6194.1</v>
+        <v>6270.34</v>
       </c>
     </row>
     <row r="157">
@@ -10032,7 +10032,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>2227.45</v>
+        <v>2257.11</v>
       </c>
     </row>
     <row r="158">
@@ -10093,7 +10093,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>1113.73</v>
+        <v>1128.55</v>
       </c>
     </row>
     <row r="159">
@@ -10154,7 +10154,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>264.51</v>
+        <v>268.03</v>
       </c>
     </row>
     <row r="160">
@@ -10215,7 +10215,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>5784.08</v>
+        <v>5861.08</v>
       </c>
     </row>
     <row r="161">
@@ -10276,7 +10276,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>11585.54</v>
+        <v>11739.78</v>
       </c>
     </row>
     <row r="162">
@@ -10337,7 +10337,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>28844.62</v>
+        <v>29228.62</v>
       </c>
     </row>
     <row r="163">
@@ -10398,7 +10398,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>11477.62</v>
+        <v>11630.42</v>
       </c>
     </row>
     <row r="164">
@@ -10459,7 +10459,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>30819.96</v>
+        <v>31230.26</v>
       </c>
     </row>
     <row r="165">
@@ -10520,7 +10520,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>499.78</v>
+        <v>506.43</v>
       </c>
     </row>
     <row r="166">
@@ -10581,7 +10581,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>303.54</v>
+        <v>307.58</v>
       </c>
     </row>
     <row r="167">
@@ -10642,7 +10642,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>2901.76</v>
+        <v>2940.39</v>
       </c>
     </row>
     <row r="168">
@@ -10703,7 +10703,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>1535.03</v>
+        <v>1555.46</v>
       </c>
     </row>
     <row r="169">
@@ -10764,7 +10764,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>607.45</v>
+        <v>615.53</v>
       </c>
     </row>
     <row r="170">
@@ -10825,7 +10825,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>10083.13</v>
+        <v>10217.36</v>
       </c>
     </row>
     <row r="171">
@@ -10886,7 +10886,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>13953.44</v>
+        <v>14139.2</v>
       </c>
     </row>
     <row r="172">
@@ -10947,7 +10947,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>15238.85</v>
+        <v>15441.72</v>
       </c>
     </row>
     <row r="173">
@@ -11008,7 +11008,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>11898.47</v>
+        <v>12056.87</v>
       </c>
     </row>
     <row r="174">
@@ -11069,7 +11069,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>3697.57</v>
+        <v>3746.8</v>
       </c>
     </row>
     <row r="175">
@@ -11130,7 +11130,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>15711.9</v>
+        <v>15921.07</v>
       </c>
     </row>
     <row r="176">
@@ -11191,7 +11191,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>556.51</v>
+        <v>563.77</v>
       </c>
     </row>
     <row r="177">
@@ -11252,7 +11252,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>5535.67</v>
+        <v>5607.91</v>
       </c>
     </row>
     <row r="178">
@@ -11313,7 +11313,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>389.8</v>
+        <v>394.89</v>
       </c>
     </row>
     <row r="179">
@@ -11374,7 +11374,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>222.75</v>
+        <v>225.65</v>
       </c>
     </row>
     <row r="180">
@@ -11435,7 +11435,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>42625.28</v>
+        <v>43181.53</v>
       </c>
     </row>
     <row r="181">
@@ -11496,7 +11496,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>28732.26</v>
+        <v>29107.2</v>
       </c>
     </row>
     <row r="182">
@@ -11557,7 +11557,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>846.4299999999999</v>
+        <v>857.48</v>
       </c>
     </row>
     <row r="183">
@@ -11618,7 +11618,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>3493.76</v>
+        <v>3539.35</v>
       </c>
     </row>
     <row r="184">
@@ -11679,7 +11679,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>9946.639999999999</v>
+        <v>10076.44</v>
       </c>
     </row>
     <row r="185">
@@ -11740,7 +11740,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>18927.29</v>
+        <v>19174.28</v>
       </c>
     </row>
     <row r="186">
@@ -11801,7 +11801,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>1146.69</v>
+        <v>1174.91</v>
       </c>
     </row>
     <row r="187">
@@ -11862,7 +11862,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>9466.68</v>
+        <v>9699.65</v>
       </c>
     </row>
     <row r="188">
@@ -11923,7 +11923,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>3512.69</v>
+        <v>3599.14</v>
       </c>
     </row>
     <row r="189">
@@ -11984,7 +11984,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>16991.13</v>
+        <v>17409.28</v>
       </c>
     </row>
     <row r="190">
@@ -12045,7 +12045,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>556.86</v>
+        <v>570.5700000000001</v>
       </c>
     </row>
     <row r="191">
@@ -12106,7 +12106,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>1670.59</v>
+        <v>1711.7</v>
       </c>
     </row>
     <row r="192">
@@ -12167,7 +12167,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>6449.82</v>
+        <v>6608.54</v>
       </c>
     </row>
     <row r="193">
@@ -12228,7 +12228,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>1559.22</v>
+        <v>1597.59</v>
       </c>
     </row>
     <row r="194">
@@ -12289,7 +12289,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>18288.76</v>
+        <v>18738.85</v>
       </c>
     </row>
     <row r="195">
@@ -12350,7 +12350,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>135819.44</v>
+        <v>139161.95</v>
       </c>
     </row>
     <row r="196">
@@ -12411,7 +12411,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>31741.22</v>
+        <v>32341.53</v>
       </c>
     </row>
     <row r="197">
@@ -12472,7 +12472,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>12459.48</v>
+        <v>12695.13</v>
       </c>
     </row>
     <row r="198">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>16705.9</v>
+        <v>17021.86</v>
       </c>
     </row>
     <row r="199">
@@ -12594,7 +12594,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>2352.19</v>
+        <v>2396.68</v>
       </c>
     </row>
     <row r="200">
@@ -12655,7 +12655,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>357.25</v>
+        <v>364.01</v>
       </c>
     </row>
     <row r="201">
@@ -12716,7 +12716,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>273.98</v>
+        <v>279.16</v>
       </c>
     </row>
     <row r="202">
@@ -12777,7 +12777,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>1113.73</v>
+        <v>1134.79</v>
       </c>
     </row>
     <row r="203">
@@ -12838,7 +12838,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>219.54</v>
+        <v>223.7</v>
       </c>
     </row>
     <row r="204">
@@ -12899,7 +12899,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>14293.7</v>
+        <v>14456.26</v>
       </c>
     </row>
     <row r="205">
@@ -12960,7 +12960,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>1372.11</v>
+        <v>1387.72</v>
       </c>
     </row>
     <row r="206">
@@ -13021,7 +13021,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>4454.91</v>
+        <v>4505.57</v>
       </c>
     </row>
     <row r="207">
@@ -13082,7 +13082,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>5115.64</v>
+        <v>5173.82</v>
       </c>
     </row>
     <row r="208">
@@ -13143,7 +13143,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>43301.37</v>
+        <v>43793.8</v>
       </c>
     </row>
     <row r="209">
@@ -13204,7 +13204,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>2228.35</v>
+        <v>2253.7</v>
       </c>
     </row>
     <row r="210">
@@ -13265,7 +13265,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>1102.59</v>
+        <v>1115.13</v>
       </c>
     </row>
     <row r="211">
@@ -13326,7 +13326,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>42279.97</v>
+        <v>42760.79</v>
       </c>
     </row>
     <row r="212">
@@ -13391,7 +13391,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>206295.33</v>
+        <v>208641.38</v>
       </c>
     </row>
     <row r="213">
@@ -13452,7 +13452,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>2793.23</v>
+        <v>2824.99</v>
       </c>
     </row>
     <row r="214">
@@ -13513,7 +13513,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>2946.96</v>
+        <v>2973.51</v>
       </c>
     </row>
     <row r="215">
@@ -13574,7 +13574,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>222.75</v>
+        <v>224.75</v>
       </c>
     </row>
     <row r="216">
@@ -13635,7 +13635,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>412.11</v>
+        <v>415.82</v>
       </c>
     </row>
     <row r="217">
@@ -13696,7 +13696,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>25628.69</v>
+        <v>25859.56</v>
       </c>
     </row>
     <row r="218">
@@ -13761,7 +13761,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>223881.38</v>
+        <v>225898.17</v>
       </c>
     </row>
     <row r="219">
@@ -13822,7 +13822,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>14734.27</v>
+        <v>14867</v>
       </c>
     </row>
     <row r="220">
@@ -13883,7 +13883,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>31741.22</v>
+        <v>32027.15</v>
       </c>
     </row>
     <row r="221">
@@ -13944,7 +13944,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>222.75</v>
+        <v>224.75</v>
       </c>
     </row>
     <row r="222">
@@ -14005,7 +14005,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>477.79</v>
+        <v>482.09</v>
       </c>
     </row>
     <row r="223">
@@ -14066,7 +14066,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>2425.77</v>
+        <v>2447.62</v>
       </c>
     </row>
     <row r="224">
@@ -14127,7 +14127,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>507.86</v>
+        <v>512.4299999999999</v>
       </c>
     </row>
     <row r="225">
@@ -14188,7 +14188,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>864.25</v>
+        <v>869.78</v>
       </c>
     </row>
     <row r="226">
@@ -14249,7 +14249,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>58192.23</v>
+        <v>58564.41</v>
       </c>
     </row>
     <row r="227">
@@ -14310,7 +14310,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>6682.36</v>
+        <v>6725.1</v>
       </c>
     </row>
     <row r="228">
@@ -14371,7 +14371,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>7796.09</v>
+        <v>7845.95</v>
       </c>
     </row>
     <row r="229">
@@ -14432,7 +14432,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>588.05</v>
+        <v>591.8099999999999</v>
       </c>
     </row>
     <row r="230">
@@ -14493,7 +14493,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>882.0700000000001</v>
+        <v>887.71</v>
       </c>
     </row>
     <row r="231">
@@ -14554,7 +14554,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>1781.96</v>
+        <v>1793.36</v>
       </c>
     </row>
     <row r="232">
@@ -14615,7 +14615,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>6547.15</v>
+        <v>6589.03</v>
       </c>
     </row>
     <row r="233">
@@ -14676,7 +14676,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>24502.48</v>
+        <v>24579.57</v>
       </c>
     </row>
     <row r="234">
@@ -14737,7 +14737,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>23190.13</v>
+        <v>23263.1</v>
       </c>
     </row>
     <row r="235">
@@ -14798,7 +14798,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>1242.92</v>
+        <v>1246.83</v>
       </c>
     </row>
     <row r="236">
@@ -14859,7 +14859,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>25615.72</v>
+        <v>25696.32</v>
       </c>
     </row>
     <row r="237">
@@ -14920,7 +14920,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>17815.82</v>
+        <v>17871.87</v>
       </c>
     </row>
     <row r="238">
@@ -14981,7 +14981,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>22663.23</v>
+        <v>22734.53</v>
       </c>
     </row>
     <row r="239">
@@ -15042,7 +15042,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>21258.68</v>
+        <v>21325.57</v>
       </c>
     </row>
     <row r="240">
@@ -15103,7 +15103,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>8801.309999999999</v>
+        <v>8829</v>
       </c>
     </row>
     <row r="241">
@@ -15164,7 +15164,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>2194.04</v>
+        <v>2200.95</v>
       </c>
     </row>
     <row r="242">
@@ -15225,7 +15225,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>400.94</v>
+        <v>402.2</v>
       </c>
     </row>
     <row r="243">
@@ -15286,7 +15286,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>133.65</v>
+        <v>134.07</v>
       </c>
     </row>
     <row r="244">
@@ -15347,7 +15347,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>16155.09</v>
+        <v>16205.92</v>
       </c>
     </row>
     <row r="245">
@@ -15408,7 +15408,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>54287</v>
+        <v>54512.01</v>
       </c>
     </row>
     <row r="246">
@@ -15469,7 +15469,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>17641.43</v>
+        <v>17714.55</v>
       </c>
     </row>
     <row r="247">
@@ -15530,7 +15530,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>11760.93</v>
+        <v>11809.67</v>
       </c>
     </row>
     <row r="248">
@@ -15591,7 +15591,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>4454.91</v>
+        <v>4473.37</v>
       </c>
     </row>
     <row r="249">
@@ -15652,7 +15652,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>51185.96</v>
+        <v>51398.12</v>
       </c>
     </row>
     <row r="250">
@@ -15713,7 +15713,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>19047.64</v>
+        <v>19126.59</v>
       </c>
     </row>
     <row r="251">
@@ -15774,7 +15774,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>46776.53</v>
+        <v>46970.41</v>
       </c>
     </row>
     <row r="252">
@@ -15835,7 +15835,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>779.46</v>
+        <v>782.6900000000001</v>
       </c>
     </row>
     <row r="253">
@@ -15896,7 +15896,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>9503.32</v>
+        <v>9542.709999999999</v>
       </c>
     </row>
     <row r="254">
@@ -15957,7 +15957,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>337.77</v>
+        <v>339.17</v>
       </c>
     </row>
     <row r="255">
@@ -16018,7 +16018,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>8416.709999999999</v>
+        <v>8451.6</v>
       </c>
     </row>
     <row r="256">
@@ -16083,7 +16083,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>76034.59</v>
+        <v>76349.73</v>
       </c>
     </row>
     <row r="257">
@@ -16144,7 +16144,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>72392.24000000001</v>
+        <v>72692.28999999999</v>
       </c>
     </row>
     <row r="258">
@@ -16205,7 +16205,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>337.77</v>
+        <v>339.17</v>
       </c>
     </row>
     <row r="259">
@@ -16266,7 +16266,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>931.61</v>
+        <v>935.47</v>
       </c>
     </row>
     <row r="260">
@@ -16327,7 +16327,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>1011.08</v>
+        <v>1015.27</v>
       </c>
     </row>
     <row r="261">
@@ -16388,7 +16388,7 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>4278.19</v>
+        <v>4295.92</v>
       </c>
     </row>
     <row r="262">
@@ -16449,7 +16449,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>117.61</v>
+        <v>117.85</v>
       </c>
     </row>
     <row r="263">
@@ -16510,7 +16510,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>529.02</v>
+        <v>530.12</v>
       </c>
     </row>
     <row r="264">
@@ -16571,7 +16571,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>4496.67</v>
+        <v>4505.99</v>
       </c>
     </row>
     <row r="265">
@@ -16632,7 +16632,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>1670.59</v>
+        <v>1674.05</v>
       </c>
     </row>
     <row r="266">
@@ -16693,7 +16693,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>26944.06</v>
+        <v>26999.88</v>
       </c>
     </row>
     <row r="267">
@@ -16754,7 +16754,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>22218.85</v>
+        <v>22264.88</v>
       </c>
     </row>
     <row r="268">
@@ -16815,7 +16815,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>35134.43</v>
+        <v>35207.21</v>
       </c>
     </row>
     <row r="269">
@@ -16876,7 +16876,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>13331.31</v>
+        <v>13358.93</v>
       </c>
     </row>
     <row r="270">
@@ -16937,7 +16937,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>60850.44</v>
+        <v>60976.5</v>
       </c>
     </row>
     <row r="271">
@@ -16998,7 +16998,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>38980.44</v>
+        <v>39061.19</v>
       </c>
     </row>
     <row r="272">
@@ -17059,7 +17059,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>8909.82</v>
+        <v>8928.27</v>
       </c>
     </row>
     <row r="273">
@@ -17120,7 +17120,7 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>2227.18</v>
+        <v>2231.79</v>
       </c>
     </row>
     <row r="274">
@@ -17181,7 +17181,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>166.96</v>
+        <v>167.3</v>
       </c>
     </row>
     <row r="275">
@@ -17242,7 +17242,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>3591.37</v>
+        <v>3598.81</v>
       </c>
     </row>
     <row r="276">
@@ -17303,7 +17303,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>58944.5</v>
+        <v>59066.6</v>
       </c>
     </row>
     <row r="277">
@@ -17364,7 +17364,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>10311.66</v>
+        <v>10333.02</v>
       </c>
     </row>
     <row r="278">
@@ -17425,7 +17425,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>1670.15</v>
+        <v>1673.61</v>
       </c>
     </row>
     <row r="279">
@@ -17486,7 +17486,7 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>79353.03999999999</v>
+        <v>79517.42999999999</v>
       </c>
     </row>
     <row r="280">
@@ -17547,7 +17547,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>23388.27</v>
+        <v>23287.79</v>
       </c>
     </row>
     <row r="281">
@@ -17608,7 +17608,7 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>38918.63</v>
+        <v>38751.44</v>
       </c>
     </row>
     <row r="282">
@@ -17669,7 +17669,7 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>24029.16</v>
+        <v>23925.93</v>
       </c>
     </row>
     <row r="283">
@@ -17730,7 +17730,7 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>9663.59</v>
+        <v>9622.07</v>
       </c>
     </row>
     <row r="284">
@@ -17791,7 +17791,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>2344.29</v>
+        <v>2334.22</v>
       </c>
     </row>
     <row r="285">
@@ -17852,7 +17852,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>27797.9</v>
+        <v>27678.48</v>
       </c>
     </row>
     <row r="286">
@@ -17913,7 +17913,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>5011.77</v>
+        <v>4990.24</v>
       </c>
     </row>
     <row r="287">
@@ -17974,7 +17974,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>7457.87</v>
+        <v>7425.83</v>
       </c>
     </row>
     <row r="288">
@@ -18035,7 +18035,7 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>31476.71</v>
+        <v>31341.49</v>
       </c>
     </row>
     <row r="289">
@@ -18096,7 +18096,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>33994.84</v>
+        <v>33848.81</v>
       </c>
     </row>
     <row r="290">
@@ -18157,7 +18157,7 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>48984.7</v>
+        <v>48774.27</v>
       </c>
     </row>
     <row r="291">
@@ -18218,7 +18218,7 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>30725.29</v>
+        <v>30593.3</v>
       </c>
     </row>
     <row r="292">
@@ -18279,7 +18279,7 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>38807.87</v>
+        <v>38641.16</v>
       </c>
     </row>
     <row r="293">
@@ -18340,7 +18340,7 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>18644.79</v>
+        <v>18564.7</v>
       </c>
     </row>
     <row r="294">
@@ -18401,7 +18401,7 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>10023.54</v>
+        <v>9980.48</v>
       </c>
     </row>
     <row r="295">
@@ -18462,7 +18462,7 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>1670.59</v>
+        <v>1663.41</v>
       </c>
     </row>
     <row r="296">
@@ -18523,7 +18523,7 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>445.48</v>
+        <v>443.57</v>
       </c>
     </row>
     <row r="297">
@@ -18584,7 +18584,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>28482.87</v>
+        <v>28360.52</v>
       </c>
     </row>
     <row r="298">
@@ -18645,7 +18645,7 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>196.02</v>
+        <v>195.17</v>
       </c>
     </row>
     <row r="299">
@@ -18706,7 +18706,7 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>1582.83</v>
+        <v>1576.03</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/administracion-y-entrega-de-beneficios/abr-2026.xlsx
+++ b/docs/oc-mensuales/administracion-y-entrega-de-beneficios/abr-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC abr-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC abr-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3847,7 +3847,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -4167,7 +4167,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4827,7 +4827,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6596,7 +6596,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -10439,7 +10439,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -11659,7 +11659,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -12147,7 +12147,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -13001,7 +13001,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -13123,7 +13123,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -13245,7 +13245,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -13382,7 +13382,7 @@
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
@@ -13752,7 +13752,7 @@
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
@@ -14595,7 +14595,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -14717,7 +14717,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -14839,7 +14839,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -14900,7 +14900,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -15327,7 +15327,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -15632,7 +15632,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -15754,7 +15754,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -16059,7 +16059,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -16074,7 +16074,7 @@
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
@@ -16246,7 +16246,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -17222,7 +17222,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -17466,7 +17466,7 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -18686,7 +18686,7 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">

--- a/docs/oc-mensuales/administracion-y-entrega-de-beneficios/abr-2026.xlsx
+++ b/docs/oc-mensuales/administracion-y-entrega-de-beneficios/abr-2026.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Car</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Car</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bienes y Servicios</t>
+          <t>Hospital de Melipilla</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
+          <t>Hospital de Constitución</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA SERENA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA SERENA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Servicio Nacional del Patrimonio Cultural</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Regimiento Logístico N° 1 "Tocopilla"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>COMISION CHILENA DE ENERGIA NUCLEAR</t>
+          <t>Comisión Chilena de Energía Nuclear</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>HOSPITAL CLAUDIO VICUNA</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4395,7 +4395,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4522,7 +4522,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5127,7 +5127,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5310,7 +5310,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5371,7 +5371,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -6042,7 +6042,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>DIRECCION REGIONAL DE ANTOFAGASTA</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6103,7 +6103,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6225,7 +6225,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6286,7 +6286,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6347,7 +6347,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO ESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6408,7 +6408,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6530,7 +6530,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6652,7 +6652,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6713,7 +6713,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Consultorio General Urbano San Felipe</t>
+          <t>CONSULTORIO GENERAL URBANO SAN FELIPE</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6774,7 +6774,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6896,7 +6896,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL DE COQUIMBO SERPAT</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -7018,7 +7018,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7079,7 +7079,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL DE COQUIMBO SERPAT</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7384,7 +7384,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7445,7 +7445,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUIRIHUE</t>
+          <t>Ilustre Municipalidad de Quirihue</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7872,7 +7872,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8055,7 +8055,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8177,7 +8177,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8299,7 +8299,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8360,7 +8360,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA CAMPO MILITAR PENALOLEN</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8482,7 +8482,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>REGIMIENTO 12 "SANGRA"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8604,7 +8604,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IX ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8665,7 +8665,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IX ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8787,7 +8787,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IX ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8848,7 +8848,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -9397,7 +9397,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XIV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9458,7 +9458,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>DIRECCION REGIONAL DE VALPARAISO DEL SNPC</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9580,7 +9580,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9641,7 +9641,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -9702,7 +9702,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -9753,7 +9753,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -10007,7 +10007,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10068,7 +10068,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -10434,7 +10434,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Curanilahue - Salud</t>
+          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -10556,7 +10556,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -10922,7 +10922,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Hospital de Achao</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -10983,7 +10983,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Servicio Nacional del Patrimonio Cultural</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -11044,7 +11044,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -11166,7 +11166,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Valdivia</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -11288,7 +11288,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -11349,7 +11349,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -11410,7 +11410,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XVI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -11593,7 +11593,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Jefatura Adm. y Log. Campo Militar La Reina</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -11715,7 +11715,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IX ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -11776,7 +11776,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -11837,7 +11837,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>COMISION CHILENA DE ENERGIA NUCLEAR</t>
+          <t>Comisión Chilena de Energía Nuclear</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -11898,7 +11898,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -12020,7 +12020,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -12081,7 +12081,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -12508,7 +12508,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Jefatura Adm. y Log. de la División Logística</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -12996,7 +12996,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -13179,7 +13179,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -13488,7 +13488,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -13732,7 +13732,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Unidad Contable Disalcar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -13919,7 +13919,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUIRIHUE</t>
+          <t>Ilustre Municipalidad de Quirihue</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -14102,7 +14102,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -14163,7 +14163,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -14529,7 +14529,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -14773,7 +14773,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -15200,7 +15200,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Departamento Provincial de Educación Osorno</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -15261,7 +15261,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Departamento Provincial de Educación Osorno</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -15383,7 +15383,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA CARAB ARAUCANÍA CONT ORD PUBL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -15444,7 +15444,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -15505,7 +15505,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -15566,7 +15566,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Escuela de Gendarmeria</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -15810,7 +15810,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Comité de Seguro Agricola</t>
+          <t>Comité de Seguros del Agro</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -16241,7 +16241,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>VIII Zona de Carabineros Bio Bío</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -16607,7 +16607,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Valparaíso</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -16973,7 +16973,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Servicio de Salud Atacama</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -17095,7 +17095,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Academia Politécnica Naval</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -17156,7 +17156,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Academia Politécnica Naval</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -17278,7 +17278,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -17339,7 +17339,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Consultorio General Urbano Victor Domingo Silva</t>
+          <t>CONSULTORIO GENERAL URBANO VICTOR DOMINGO SILVA</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -17400,7 +17400,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA CAMPO MILITAR PENALOLEN</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -17644,7 +17644,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -17771,7 +17771,7 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -17827,7 +17827,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -17888,7 +17888,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>COMISION CHILENA DE ENERGIA NUCLEAR</t>
+          <t>Comisión Chilena de Energía Nuclear</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -18076,7 +18076,7 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -18198,7 +18198,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -18437,7 +18437,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -18498,7 +18498,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -18620,7 +18620,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">

--- a/docs/oc-mensuales/administracion-y-entrega-de-beneficios/abr-2026.xlsx
+++ b/docs/oc-mensuales/administracion-y-entrega-de-beneficios/abr-2026.xlsx
@@ -562,7 +562,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1082,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1147,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1212,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1277,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1342,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1407,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1472,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1537,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1602,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1667,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1732,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1797,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1862,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1927,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1992,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2057,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2122,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2187,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2252,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2317,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2382,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2447,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2512,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2518,7 +2642,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2579,7 +2707,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2640,7 +2772,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2701,7 +2837,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2762,7 +2902,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2823,7 +2967,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2884,7 +3032,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2945,7 +3097,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3006,7 +3162,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3067,7 +3227,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3128,7 +3292,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3189,7 +3357,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3250,7 +3422,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3311,7 +3487,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3372,7 +3552,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3433,7 +3617,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3494,7 +3682,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3555,7 +3747,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3616,7 +3812,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3677,7 +3877,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3738,7 +3942,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3799,7 +4007,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3860,7 +4072,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3921,7 +4137,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3982,7 +4202,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4043,7 +4267,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4104,7 +4332,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4230,7 +4462,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4291,7 +4527,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4352,7 +4592,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4413,7 +4657,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4474,7 +4722,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4535,7 +4787,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4596,7 +4852,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4657,7 +4917,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4718,7 +4982,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4779,7 +5047,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4840,7 +5112,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4901,7 +5177,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4962,7 +5242,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5023,7 +5307,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5084,7 +5372,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5145,7 +5437,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5206,7 +5502,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5267,7 +5567,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5328,7 +5632,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5389,7 +5697,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5450,7 +5762,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5511,7 +5827,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5572,7 +5892,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5633,7 +5957,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5694,7 +6022,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5755,7 +6087,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5816,7 +6152,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5877,7 +6217,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5938,7 +6282,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5999,7 +6347,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6060,7 +6412,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6121,7 +6477,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6182,7 +6542,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6243,7 +6607,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6304,7 +6672,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6365,7 +6737,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6426,7 +6802,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6487,7 +6867,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6548,7 +6932,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6609,7 +6997,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6670,7 +7062,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6731,7 +7127,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6792,7 +7192,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6853,7 +7257,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6914,7 +7322,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6975,7 +7387,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7036,7 +7452,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7097,7 +7517,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7158,7 +7582,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7219,7 +7647,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7280,7 +7712,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7341,7 +7777,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7402,7 +7842,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7463,7 +7907,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7524,7 +7972,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7585,7 +8037,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7646,7 +8102,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7707,7 +8167,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7768,7 +8232,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7829,7 +8297,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7890,7 +8362,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7951,7 +8427,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8012,7 +8492,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8073,7 +8557,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8134,7 +8622,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8195,7 +8687,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8256,7 +8752,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8317,7 +8817,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8378,7 +8882,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8439,7 +8947,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8500,7 +9012,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8561,7 +9077,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8622,7 +9142,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8683,7 +9207,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8744,7 +9272,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8805,7 +9337,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8866,7 +9402,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8927,7 +9467,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8988,7 +9532,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9049,7 +9597,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9110,7 +9662,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9171,7 +9727,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9232,7 +9792,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9293,7 +9857,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9354,7 +9922,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9415,7 +9987,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9476,7 +10052,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9537,7 +10117,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9598,7 +10182,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9659,7 +10247,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9720,7 +10312,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9781,7 +10377,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9842,7 +10442,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9903,7 +10507,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9964,7 +10572,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10025,7 +10637,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10086,7 +10702,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10147,7 +10767,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10208,7 +10832,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10269,7 +10897,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10330,7 +10962,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10391,7 +11027,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10452,7 +11092,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10513,7 +11157,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10574,7 +11222,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10635,7 +11287,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10696,7 +11352,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10757,7 +11417,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10818,7 +11482,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10879,7 +11547,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10940,7 +11612,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11001,7 +11677,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11062,7 +11742,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11123,7 +11807,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11184,7 +11872,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11245,7 +11937,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11306,7 +12002,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11367,7 +12067,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11428,7 +12132,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11489,7 +12197,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11550,7 +12262,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11611,7 +12327,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11672,7 +12392,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11733,7 +12457,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11794,7 +12522,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11855,7 +12587,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11916,7 +12652,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11977,7 +12717,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12038,7 +12782,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12099,7 +12847,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12160,7 +12912,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12221,7 +12977,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12282,7 +13042,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12343,7 +13107,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12404,7 +13172,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12465,7 +13237,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12526,7 +13302,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12587,7 +13367,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12648,7 +13432,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12709,7 +13497,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12770,7 +13562,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12831,7 +13627,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12892,7 +13692,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12953,7 +13757,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13014,7 +13822,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13075,7 +13887,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13136,7 +13952,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13197,7 +14017,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13258,7 +14082,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13319,7 +14147,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13445,7 +14277,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13506,7 +14342,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13567,7 +14407,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13628,7 +14472,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13689,7 +14537,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13815,7 +14667,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13876,7 +14732,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13937,7 +14797,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13998,7 +14862,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14059,7 +14927,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14120,7 +14992,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14181,7 +15057,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14242,7 +15122,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14303,7 +15187,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14364,7 +15252,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14425,7 +15317,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14486,7 +15382,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14547,7 +15447,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14608,7 +15512,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14669,7 +15577,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14730,7 +15642,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14791,7 +15707,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14852,7 +15772,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14913,7 +15837,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14974,7 +15902,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15035,7 +15967,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15096,7 +16032,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15157,7 +16097,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15218,7 +16162,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15279,7 +16227,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15340,7 +16292,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15401,7 +16357,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15462,7 +16422,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15523,7 +16487,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15584,7 +16552,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15645,7 +16617,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15706,7 +16682,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15767,7 +16747,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15828,7 +16812,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15889,7 +16877,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15950,7 +16942,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16011,7 +17007,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16137,7 +17137,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16198,7 +17202,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16259,7 +17267,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16320,7 +17332,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16381,7 +17397,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16442,7 +17462,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16503,7 +17527,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16564,7 +17592,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16625,7 +17657,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16686,7 +17722,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16747,7 +17787,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16808,7 +17852,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16869,7 +17917,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16930,7 +17982,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16991,7 +18047,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17052,7 +18112,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17113,7 +18177,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17174,7 +18242,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17235,7 +18307,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17296,7 +18372,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr"/>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L276" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17357,7 +18437,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17418,7 +18502,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17479,7 +18567,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17540,7 +18632,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17601,7 +18697,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17662,7 +18762,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr"/>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17723,7 +18827,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17784,7 +18892,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr"/>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L284" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17845,7 +18957,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17906,7 +19022,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr"/>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L286" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17967,7 +19087,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18028,7 +19152,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18089,7 +19217,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18150,7 +19282,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L290" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18211,7 +19347,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18272,7 +19412,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18333,7 +19477,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18394,7 +19542,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18455,7 +19607,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18516,7 +19672,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18577,7 +19737,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18638,7 +19802,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18699,7 +19867,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L299" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/administracion-y-entrega-de-beneficios/abr-2026.xlsx
+++ b/docs/oc-mensuales/administracion-y-entrega-de-beneficios/abr-2026.xlsx
@@ -6254,7 +6254,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -19839,7 +19839,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
